--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104633_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104633_W20.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>D. ENNIS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4198</v>
+        <v>4.9064</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9264</v>
+        <v>2.9331</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4934</v>
+        <v>1.9733</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0298</v>
+        <v>6.1743</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7419</v>
+        <v>2.2837</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2879</v>
+        <v>3.8906</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9564</v>
+        <v>5.4838</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8072</v>
+        <v>2.3712</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1493</v>
+        <v>3.1126</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.6905</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0653</v>
+        <v>-0.0876</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1387</v>
+        <v>0.778</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9078</v>
+        <v>-0.4272</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6635</v>
+        <v>-0.2257</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2443</v>
+        <v>-0.2016</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4822</v>
+        <v>-0.1578</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5748</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. ENNIS</t>
+          <t>K. MARTIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6285</v>
+        <v>3.2042</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2667</v>
+        <v>2.7791</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3618</v>
+        <v>0.425</v>
       </c>
       <c r="G3" t="n">
-        <v>6.187</v>
+        <v>1.8108</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2901</v>
+        <v>1.2895</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8969</v>
+        <v>0.5213</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5322</v>
+        <v>1.5656</v>
       </c>
       <c r="K3" t="n">
-        <v>2.403</v>
+        <v>1.0892</v>
       </c>
       <c r="L3" t="n">
-        <v>3.1292</v>
+        <v>0.4764</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6548</v>
+        <v>0.2452</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.113</v>
+        <v>0.2003</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7678</v>
+        <v>0.0449</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4025</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>2.722</v>
+        <v>0.6829</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7173</v>
+        <v>-0.3205</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9557</v>
+        <v>-0.193</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.1275</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1607</v>
+        <v>1.2586</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2534</v>
+        <v>-0.3757</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. MARTIN</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5522</v>
+        <v>2.8557</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0865</v>
+        <v>1.5756</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4657</v>
+        <v>1.2802</v>
       </c>
       <c r="G4" t="n">
-        <v>1.811</v>
+        <v>2.0222</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2885</v>
+        <v>1.7269</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5224</v>
+        <v>0.2953</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5836</v>
+        <v>1.9201</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1012</v>
+        <v>1.7712</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4824</v>
+        <v>0.1489</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2274</v>
+        <v>0.1021</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1874</v>
+        <v>-0.0442</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04</v>
+        <v>0.1463</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0278</v>
+        <v>0.3602</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0907</v>
+        <v>0.369</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0629</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2598</v>
+        <v>0.4733</v>
       </c>
       <c r="W4" t="n">
-        <v>1.639</v>
+        <v>1.5628</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3793</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.114</v>
+        <v>2.6602</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2484</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8656</v>
+        <v>1.7605</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1128</v>
+        <v>2.1235</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0359</v>
+        <v>1.0449</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0769</v>
+        <v>1.0786</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8695</v>
+        <v>1.8638</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6754</v>
+        <v>0.6722</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1941</v>
+        <v>1.1916</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2433</v>
+        <v>0.2597</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2256</v>
+        <v>0.309</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4869</v>
+        <v>0.174</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2613</v>
+        <v>0.135</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. FALK</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1356</v>
+        <v>1.3799</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7534</v>
+        <v>-1.0919</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6179</v>
+        <v>2.4718</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8571</v>
+        <v>5.1181</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6896</v>
+        <v>-0.5921</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1675</v>
+        <v>5.7102</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8993</v>
+        <v>3.854</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6754</v>
+        <v>-1.1796</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2239</v>
+        <v>5.0335</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9578</v>
+        <v>1.2641</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0142</v>
+        <v>0.5875</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9436</v>
+        <v>0.6766</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2683</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.6421</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2683</v>
+        <v>3.1868</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8045</v>
+        <v>-1.5885</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3992</v>
+        <v>-0.5298</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4053</v>
+        <v>-1.0587</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1853</v>
+        <v>-1.6943</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2534</v>
+        <v>-0.7739</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.4387</v>
+        <v>-0.9204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>W. FALK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9425</v>
+        <v>1.2998</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9278999999999999</v>
+        <v>1.8826</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8704</v>
+        <v>-0.5828</v>
       </c>
       <c r="G7" t="n">
-        <v>3.0888</v>
+        <v>1.8712</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5066</v>
+        <v>0.7002</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5954</v>
+        <v>1.171</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5413</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.2276</v>
+        <v>0.6722</v>
       </c>
       <c r="L7" t="n">
-        <v>3.769</v>
+        <v>0.2234</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5475</v>
+        <v>0.9755</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7211</v>
+        <v>0.028</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8264</v>
+        <v>0.9476</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.6293</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.722</v>
+        <v>2.2763</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0205</v>
+        <v>-0.6688</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0253</v>
+        <v>-0.2603</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0048</v>
+        <v>-0.4085</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2185</v>
+        <v>-2.1789</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1853</v>
+        <v>1.2472</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4039</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.65</v>
+        <v>1.0023</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4048</v>
+        <v>-1.616</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0548</v>
+        <v>2.6183</v>
       </c>
       <c r="G8" t="n">
-        <v>5.133</v>
+        <v>1.8079</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6004</v>
+        <v>0.4109</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7334</v>
+        <v>1.397</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>1.319</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1642</v>
+        <v>0.4407</v>
       </c>
       <c r="L8" t="n">
-        <v>5.0643</v>
+        <v>0.8783</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2329</v>
+        <v>0.4889</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5638</v>
+        <v>-0.0298</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6691</v>
+        <v>0.5187</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.6293</v>
+        <v>-4.5526</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1757</v>
+        <v>2.2763</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.3324</v>
+        <v>-0.0057</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9043</v>
+        <v>-0.0166</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.4282</v>
+        <v>0.0108</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.6968</v>
+        <v>1.4764</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7712</v>
+        <v>1.6342</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9256</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. SEVILLA</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.441</v>
+        <v>0.8853</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0176</v>
+        <v>-0.5283</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4586</v>
+        <v>1.4136</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0361</v>
+        <v>3.0959</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1212</v>
+        <v>-1.4996</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1573</v>
+        <v>4.5955</v>
       </c>
       <c r="J9" t="n">
-        <v>0.052</v>
+        <v>1.5159</v>
       </c>
       <c r="K9" t="n">
-        <v>0.052</v>
+        <v>-2.245</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.7609</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0159</v>
+        <v>1.58</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1732</v>
+        <v>0.7454</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1573</v>
+        <v>0.8345</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.6421</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>2.7316</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0487</v>
+        <v>-1.0821</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0696</v>
+        <v>-0.581</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0209</v>
+        <v>-0.5011</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2179</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.3968</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>P. SEVILLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2089</v>
+        <v>0.4751</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8971</v>
+        <v>-0.018</v>
       </c>
       <c r="F10" t="n">
-        <v>2.106</v>
+        <v>0.4931</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6253</v>
+        <v>0.0373</v>
       </c>
       <c r="H10" t="n">
-        <v>0.955</v>
+        <v>-0.1207</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5803</v>
+        <v>0.1579</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0291</v>
+        <v>0.0517</v>
       </c>
       <c r="K10" t="n">
-        <v>0.218</v>
+        <v>0.0517</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2471</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4038</v>
+        <v>-0.0144</v>
       </c>
       <c r="N10" t="n">
-        <v>0.737</v>
+        <v>-0.1724</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3331</v>
+        <v>0.1579</v>
       </c>
       <c r="P10" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0796</v>
+        <v>-0.0174</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1875</v>
+        <v>-0.0697</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1079</v>
+        <v>0.0523</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5527</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.0593</v>
+        <v>0.3828</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3605</v>
+        <v>-1.5399</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3012</v>
+        <v>1.9227</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8162</v>
+        <v>-1.6147</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4142</v>
+        <v>0.9699</v>
       </c>
       <c r="I11" t="n">
-        <v>1.402</v>
+        <v>-2.5847</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3537</v>
+        <v>-2.0471</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4636</v>
+        <v>0.2101</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8902</v>
+        <v>-2.2572</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4625</v>
+        <v>0.4324</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0494</v>
+        <v>0.7598</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5118</v>
+        <v>-0.3275</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2683</v>
+        <v>1.3658</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5367</v>
+        <v>-0.2276</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0855</v>
+        <v>0.0757</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8166</v>
+        <v>0.1901</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2689</v>
+        <v>-0.1144</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4783</v>
+        <v>0.5561</v>
       </c>
       <c r="W11" t="n">
-        <v>1.639</v>
+        <v>0.5447</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>0.0113</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3942</v>
+        <v>-2.0249</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2038</v>
+        <v>-4.7713</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8096</v>
+        <v>2.7464</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1742</v>
+        <v>-2.1685</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.2005</v>
+        <v>-3.1995</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0263</v>
+        <v>1.031</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.5294</v>
+        <v>-3.5469</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.8279</v>
+        <v>-3.8448</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2985</v>
+        <v>0.2979</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3551</v>
+        <v>1.3784</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6274</v>
+        <v>0.6452</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4788</v>
+        <v>-0.1637</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6866</v>
+        <v>0.1414</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2078</v>
+        <v>-0.305</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3793</v>
+        <v>-0.3757</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3793</v>
+        <v>-0.3757</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.639</v>
+        <v>17.0268</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5302999999999995</v>
+        <v>0.5046999999999997</v>
       </c>
       <c r="F13" t="n">
-        <v>16.1692</v>
+        <v>16.5221</v>
       </c>
       <c r="G13" t="n">
-        <v>20.2723</v>
+        <v>20.278</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9865</v>
+        <v>3.0141</v>
       </c>
       <c r="I13" t="n">
-        <v>17.2857</v>
+        <v>17.2637</v>
       </c>
       <c r="J13" t="n">
-        <v>13.1295</v>
+        <v>12.8756</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1761000000000013</v>
+        <v>0.009100000000000108</v>
       </c>
       <c r="L13" t="n">
-        <v>12.9538</v>
+        <v>12.8663</v>
       </c>
       <c r="M13" t="n">
-        <v>7.142600000000002</v>
+        <v>7.4024</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8105</v>
+        <v>3.0049</v>
       </c>
       <c r="O13" t="n">
-        <v>4.332100000000001</v>
+        <v>4.397100000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-20.4149</v>
+        <v>-20.4868</v>
       </c>
       <c r="R13" t="n">
-        <v>21.5491</v>
+        <v>21.625</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.8997</v>
+        <v>-3.529</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.404300000000001</v>
+        <v>-1.0016</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.4955</v>
+        <v>-2.5275</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8675999999999999</v>
+        <v>-0.8601999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>9.1593</v>
+        <v>9.117600000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.0272</v>
+        <v>-9.978</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. LIMA</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7718</v>
+        <v>2.7091</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6289</v>
+        <v>1.764</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1429</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3117</v>
+        <v>2.8115</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3117</v>
+        <v>2.5907</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.2208</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0346</v>
+        <v>2.8529</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0346</v>
+        <v>2.7784</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.0745</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3463</v>
+        <v>-0.0414</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3463</v>
+        <v>-0.1877</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.1463</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4537</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6979</v>
+        <v>-0.4275</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4336</v>
+        <v>-0.4743</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2643</v>
+        <v>0.0468</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9320000000000001</v>
+        <v>-1.0407</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1607</v>
+        <v>-0.387</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7712</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>J. RUBIO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8332</v>
+        <v>1.7517</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0779</v>
+        <v>-0.091</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7554</v>
+        <v>1.8427</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8049</v>
+        <v>0.8104</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5916</v>
+        <v>0.307</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2133</v>
+        <v>0.5034</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8728</v>
+        <v>0.4364</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7982</v>
+        <v>0.0345</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0746</v>
+        <v>0.4019</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.068</v>
+        <v>0.374</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2066</v>
+        <v>0.2725</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1387</v>
+        <v>0.1014</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2914</v>
+        <v>-0.1789</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1825</v>
+        <v>-0.2998</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1089</v>
+        <v>0.1209</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0412</v>
+        <v>0.665</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6556</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. RUBIO</t>
+          <t>A. LIMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3447</v>
+        <v>1.7084</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2018</v>
+        <v>0.6845</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5465</v>
+        <v>1.0239</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8079</v>
+        <v>-0.3103</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3015</v>
+        <v>-0.3103</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5064</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4424</v>
+        <v>0.0345</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4078</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3655</v>
+        <v>-0.3447</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2669</v>
+        <v>-0.3447</v>
       </c>
       <c r="O16" t="n">
-        <v>0.09859999999999999</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5789</v>
+        <v>0.6317</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4174</v>
+        <v>0.4923</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1615</v>
+        <v>0.1394</v>
       </c>
       <c r="V16" t="n">
-        <v>0.662</v>
+        <v>0.9317</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
-        <v>0.662</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0809</v>
+        <v>1.1605</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2995</v>
+        <v>1.0674</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2186</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6879</v>
+        <v>-1.6684</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2206</v>
+        <v>0.232</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.9085</v>
+        <v>-1.9004</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2651</v>
+        <v>0.2641</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1905</v>
+        <v>0.1896</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.953</v>
+        <v>-1.9325</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.9831</v>
+        <v>-1.9749</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0468</v>
+        <v>1.0973</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0344</v>
+        <v>0.8033</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0124</v>
+        <v>0.294</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6482</v>
+        <v>0.7977</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4496</v>
+        <v>0.6835</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1985</v>
+        <v>0.1142</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1784</v>
+        <v>-0.1744</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0375</v>
+        <v>0.0401</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7672</v>
+        <v>-0.7604</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1461</v>
+        <v>0.2892</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1391</v>
+        <v>0.0975</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2852</v>
+        <v>0.1917</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3242</v>
+        <v>-0.0146</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2187</v>
+        <v>-1.1357</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8945</v>
+        <v>1.1211</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7245</v>
+        <v>1.7289</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6045</v>
+        <v>1.6082</v>
       </c>
       <c r="I19" t="n">
-        <v>0.12</v>
+        <v>0.1207</v>
       </c>
       <c r="J19" t="n">
-        <v>2.507</v>
+        <v>2.4861</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4648</v>
+        <v>1.4511</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0422</v>
+        <v>1.035</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7825</v>
+        <v>-0.7573</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1397</v>
+        <v>0.157</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R19" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1001</v>
+        <v>0.2078</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2571</v>
+        <v>-0.1375</v>
       </c>
       <c r="U19" t="n">
-        <v>0.157</v>
+        <v>0.3452</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0412</v>
+        <v>-1.0407</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="20">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7866</v>
+        <v>-0.9009</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7889</v>
+        <v>-0.8506</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0023</v>
+        <v>-0.0503</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.7869</v>
+        <v>-4.8007</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3652</v>
+        <v>1.3561</v>
       </c>
       <c r="I20" t="n">
-        <v>-6.1521</v>
+        <v>-6.1568</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8031</v>
+        <v>-1.85</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0913</v>
+        <v>2.0609</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.8945</v>
+        <v>-3.911</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.9838</v>
+        <v>-2.9506</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7261</v>
+        <v>-0.7048</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.2576</v>
+        <v>-2.2458</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S20" t="n">
-        <v>0.881</v>
+        <v>0.7907</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3902</v>
+        <v>0.3943</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4908</v>
+        <v>0.3964</v>
       </c>
       <c r="V20" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="W20" t="n">
-        <v>2.8924</v>
+        <v>2.8814</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7229</v>
+        <v>-1.5181</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3069</v>
+        <v>-3.4969</v>
       </c>
       <c r="F21" t="n">
-        <v>1.584</v>
+        <v>1.9788</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3163</v>
+        <v>-2.3325</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.469</v>
+        <v>-0.4682</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8473</v>
+        <v>-1.8643</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.6834</v>
+        <v>-1.7347</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0328</v>
+        <v>-1.0557</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6506</v>
+        <v>-0.679</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6329</v>
+        <v>-0.5977</v>
       </c>
       <c r="N21" t="n">
-        <v>0.5638</v>
+        <v>0.5875</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8783</v>
+        <v>1.1101</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4083</v>
+        <v>0.2944</v>
       </c>
       <c r="U21" t="n">
-        <v>0.47</v>
+        <v>0.8157</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5297</v>
+        <v>1.5253</v>
       </c>
       <c r="W21" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4432</v>
+        <v>-3.7581</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6082</v>
+        <v>-1.9764</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.835</v>
+        <v>-1.7817</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2055</v>
+        <v>-2.1962</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1025</v>
+        <v>-0.1006</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.103</v>
+        <v>-2.0956</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6625</v>
+        <v>-0.6662</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6998</v>
+        <v>-0.7035</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5431</v>
+        <v>-1.53</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.1404</v>
+        <v>-2.1328</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5108</v>
+        <v>0.1892</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2299</v>
+        <v>-0.1233</v>
       </c>
       <c r="U22" t="n">
-        <v>0.281</v>
+        <v>0.3126</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9547</v>
+        <v>-4.2836</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8698</v>
+        <v>-4.33</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0849</v>
+        <v>0.0464</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.9728</v>
+        <v>-4.9811</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.6561</v>
+        <v>-3.6752</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3167</v>
+        <v>-1.3059</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.9158</v>
+        <v>-3.9529</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.9531</v>
+        <v>-3.9902</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.057</v>
+        <v>-1.0282</v>
       </c>
       <c r="N23" t="n">
-        <v>0.297</v>
+        <v>0.3149</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0765</v>
+        <v>0.6097</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0998</v>
+        <v>0.4943</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0233</v>
+        <v>0.1154</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9722</v>
+        <v>-4.6562</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2182</v>
+        <v>-2.1812</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.754</v>
+        <v>-2.475</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.2398</v>
+        <v>-3.2355</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4704</v>
+        <v>-0.471</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.7694</v>
+        <v>-2.7645</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6101</v>
+        <v>-0.628</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1763</v>
+        <v>0.1616</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.6298</v>
+        <v>-2.6075</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.9831</v>
+        <v>-1.9749</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2787</v>
+        <v>0.0346</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8861</v>
+        <v>0.1784</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3926</v>
+        <v>-0.1438</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.1138</v>
+        <v>-7.8391</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.5054</v>
+        <v>-7.7493</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3916</v>
+        <v>-0.0898</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.9101</v>
+        <v>-5.9296</v>
       </c>
       <c r="H25" t="n">
-        <v>-4.0976</v>
+        <v>-4.1229</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.8125</v>
+        <v>-1.8066</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.1785</v>
+        <v>-5.2304</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.5041</v>
+        <v>-4.5525</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.7316</v>
+        <v>-0.6992</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4065</v>
+        <v>0.4296</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.1381</v>
+        <v>-1.1287</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R25" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S25" t="n">
-        <v>3.0644</v>
+        <v>1.3587</v>
       </c>
       <c r="T25" t="n">
-        <v>1.981</v>
+        <v>0.8077</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0833</v>
+        <v>0.551</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.1339</v>
+        <v>-2.1301</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.4553</v>
+        <v>-2.4457</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-15.6388</v>
+        <v>-14.8432</v>
       </c>
       <c r="E26" t="n">
-        <v>-17.262</v>
+        <v>-17.6117</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6232</v>
+        <v>2.7686</v>
       </c>
       <c r="G26" t="n">
-        <v>-20.2721</v>
+        <v>-20.2779</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.9864</v>
+        <v>-3.0141</v>
       </c>
       <c r="I26" t="n">
-        <v>-17.2857</v>
+        <v>-17.2636</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.1427</v>
+        <v>-7.402100000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.8107</v>
+        <v>-3.005200000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>-4.3321</v>
+        <v>-4.3972</v>
       </c>
       <c r="M26" t="n">
-        <v>-13.1297</v>
+        <v>-12.8755</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.1757000000000001</v>
+        <v>-0.009100000000000052</v>
       </c>
       <c r="O26" t="n">
-        <v>-12.9538</v>
+        <v>-12.8665</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.1341</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q26" t="n">
-        <v>-21.5489</v>
+        <v>-21.6249</v>
       </c>
       <c r="R26" t="n">
-        <v>20.415</v>
+        <v>20.4868</v>
       </c>
       <c r="S26" t="n">
-        <v>4.8997</v>
+        <v>5.7126</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4954</v>
+        <v>2.5273</v>
       </c>
       <c r="U26" t="n">
-        <v>2.4043</v>
+        <v>3.1853</v>
       </c>
       <c r="V26" t="n">
-        <v>0.8679000000000006</v>
+        <v>0.8602000000000012</v>
       </c>
       <c r="W26" t="n">
-        <v>8.934400000000002</v>
+        <v>8.888400000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-8.066599999999999</v>
+        <v>-8.0282</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104633_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104633_W20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.3757</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.9204</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.3968</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0.0113</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.3757</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-9.978</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.665</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.4457</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104633_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-8.0282</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
